--- a/tests/sample_data/GlobalCatch_Flag_Gear_CCSBT.xlsx
+++ b/tests/sample_data/GlobalCatch_Flag_Gear_CCSBT.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -430,79 +430,1100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Catches are presented as whole weights in tonnes.  All figures, particularly for the last reported year of catch are subject to change as improved data or estimates become available.</t>
+          <t>Please note that for most Members, their quota year / fishing season is different from the calendar year and that the reported catch will therefore differ according to the timescale used.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Please note that for most Members, their quota year / fishing season is different from the calendar year and that the reported catch will therefore differ according to the timescale used.</t>
+          <t>1954</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2447</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Note:  reviews of SBT data in 2006 indicated that southern bluefin tuna catches may have been substantially under-reported over the previous 10-20 years and the data presented here do not yet include estimates for this unreported catch.</t>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9603</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1957</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>22908</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1960</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>75826</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Korea*</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>European_x000D_
-Community</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Research &amp; Other</t>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4636</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>40397</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>723.8</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8679</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>49769</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12672</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>34005</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>10783</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>27828</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4.0922200000000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>16843</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>27981</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>14.21683</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>17695</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>24881</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>7.1287599999999998</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>10820.763000000001</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>7.0644</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10590.944</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>11422</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2.0251100000000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4488.6440000000002</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6477</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>164.483</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>246.1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>758.5</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>96.636799999999994</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5634.8401999999996</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4207</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>238.244</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>149.5</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50.406799999999997</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>597.88905999999997</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>15.1974</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>5.2961900000000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5824.0591899999999</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4745</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>922.29</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1050.5723800000001</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1162</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>592.94899999999996</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>62.884799999999998</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6400.8665700000001</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>5945</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1008.009</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1268.4282599999999</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1086.614</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>207.13224</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.8651</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5459.0177000000003</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6452</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>787.947</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>57.2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1241</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1274</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1122.7150999999999</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>161.27289999999999</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0.43640000000000001</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>6216.1356800000003</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6505</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>890.85400000000004</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>57.48</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1512</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1224.3765000000001</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>243.76738</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0.43809999999999999</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>*:</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Japanese Import Statistics for 1993, 1994, and 1998 are higher than these official statistics and are:</t>
         </is>
       </c>
     </row>
@@ -513,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -522,25 +1543,774 @@
           <t>Global Southern Bluefin Tuna Catch by Gear</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>...2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>...4</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>...5</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>...6</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>...7</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>...8</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Catches are presented as whole weights in tonnes.  All figures, particularly for the last reported year of catch are subject to change as improved data or estimates become available.</t>
+          <t>Note:  reviews of SBT data in 2006 indicated that southern bluefin tuna catches may have been substantially under-reported over the previous 10-20 years and the data presented here do not yet include estimates for this unreported catch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1964</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>321.999999963768</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Catches from Indonesia and the "Misc" category of flags were assigned to the longline fishery.  Catches from other line fisheries not listed below (such as "minor line") were also assigned to the longline fishery.</t>
+          <t>1957</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>22908</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1263.99999975279</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1958</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12462</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2322.0000006119199</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Note:  reviews of SBT data in 2006 indicated that southern bluefin tuna catches may have been substantially under-reported over the previous 10-20 years and the data presented here do not yet include estimates for this unreported catch.</t>
+          <t>1960</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>75826</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3545.0000008365701</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>41120.800000000003</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4636.0000019305498</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>40691.000010830998</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6875.9999998339099</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>41058.999998245199</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7097.0000009385203</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>33729.1141953685</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2036.2077308436701</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9158.7922691563108</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15624.920857352299</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6376.1070067787996</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6155.2869932211397</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>81.000157587999993</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12227.0792925185</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2819.6261914185902</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>7770.2628085814104</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>234.00082009600001</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12466.716609036301</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>22.450318560551999</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1672.54368143944</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4.4069244320000003</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>47.828669087000002</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2.9999950900000001</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11271.1454753502</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1840.1584610831001</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>794.76153891689705</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>9.0121860550000008</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>16.742629870999998</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10572.402912863299</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4683.4292800000003</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.0468</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.69860644900000002</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5782.3064228435896</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4808.8844251931096</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.18775</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3.764279964</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4.0250000000000004</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7728.9594463473104</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4168.0860562656499</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>9.5381049618475799</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.2172022280000001</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1.3340000000000001</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>9106.6500564796497</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5251.7364494965204</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.81224799837550399</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.55661742508744005</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11757.844278070301</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5366.6392564547205</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>9.4835759034541702</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0.2291</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>14.018959999833999</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>11426.8925711253</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5249.2570358737403</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.3175597054655901</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>28.0631388729186</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>380.880521591057</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>13527.580113723299</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4393.5427109390002</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1.5675345270000001</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>4.2743380799999997</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0.85843702799999999</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>440.22852640000002</t>
         </is>
       </c>
     </row>
